--- a/results/Int Task Remove ACC 0.4/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC 0.4/Rando_9_permute.xlsx
@@ -440,707 +440,707 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6237485759657542</v>
+        <v>0.6395956318109113</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6236661066424245</v>
+        <v>0.6395956318109113</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6219869928616089</v>
+        <v>0.6384741449081905</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6219869928616089</v>
+        <v>0.6420088184639225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6171136312202008</v>
+        <v>0.6413394744210845</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6393721974814253</v>
+        <v>0.6413394744210845</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6471108886357273</v>
+        <v>0.643582448226526</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.648232375538448</v>
+        <v>0.6396603606402689</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.648232375538448</v>
+        <v>0.6382276958838218</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.656176760528264</v>
+        <v>0.6368420194627603</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6445337222816768</v>
+        <v>0.6339766899498663</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6449273694587327</v>
+        <v>0.6461188593917216</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6335485207304864</v>
+        <v>0.6511801743746716</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6424734276168667</v>
+        <v>0.6511801743746716</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6409175383482353</v>
+        <v>0.6527538041372749</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6154417095315359</v>
+        <v>0.6616609705296832</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6108680183964128</v>
+        <v>0.6629996586153593</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6160055695561616</v>
+        <v>0.6658649881282532</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5720575712592491</v>
+        <v>0.6658649881282532</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5729378833385117</v>
+        <v>0.6697400873791248</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5654288596602264</v>
+        <v>0.6711257638001864</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5864196998116631</v>
+        <v>0.6480329148494648</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5894552421721269</v>
+        <v>0.6540277633935935</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5788689619989029</v>
+        <v>0.6516677982224983</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5807715101092048</v>
+        <v>0.632755952175464</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5687170841915897</v>
+        <v>0.6271662581558326</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.564524573940461</v>
+        <v>0.6081019397552003</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5661744398798634</v>
+        <v>0.6059999309559153</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5695389005880255</v>
+        <v>0.6485622528317664</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5668907722580868</v>
+        <v>0.6392854129028052</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5705194224845898</v>
+        <v>0.6379467248171291</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.571499944381154</v>
+        <v>0.6648437110428342</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5675486089534835</v>
+        <v>0.664644250353851</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5867716328542441</v>
+        <v>0.6595891685174318</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5873939885616967</v>
+        <v>0.6365912551831011</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5494000836200581</v>
+        <v>0.6415116051598946</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.548267089369896</v>
+        <v>0.6415116051598946</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5140490328074475</v>
+        <v>0.6301912521144751</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5149825663686264</v>
+        <v>0.6608755940668116</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5114594001603356</v>
+        <v>0.6504657598876883</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5238772664679732</v>
+        <v>0.6370026428541291</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5558470750240696</v>
+        <v>0.6475241941979955</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5507387717057342</v>
+        <v>0.6478353720517217</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5132094759170397</v>
+        <v>0.6372490918784978</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5145481640027157</v>
+        <v>0.6046444613218873</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5301602781709455</v>
+        <v>0.6149373041353571</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5117005749837938</v>
+        <v>0.6227344909724859</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5083068664342183</v>
+        <v>0.6383935934761011</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5075905340559947</v>
+        <v>0.6220004181002904</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5133859219111403</v>
+        <v>0.6325804651269836</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5205554788399059</v>
+        <v>0.5784105859924895</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5205554788399059</v>
+        <v>0.6127998143481279</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5205084905045205</v>
+        <v>0.5920218601243561</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5299147880921968</v>
+        <v>0.5700452238754444</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5278127792929118</v>
+        <v>0.5959794286985574</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5222700736086658</v>
+        <v>0.6053502452982896</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5222700736086658</v>
+        <v>0.6073112890914182</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5183949743577941</v>
+        <v>0.6073112890914182</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5174144524612299</v>
+        <v>0.6078104202866864</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5216654583951853</v>
+        <v>0.6099531842748261</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5216654583951853</v>
+        <v>0.6027721199986191</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5216654583951853</v>
+        <v>0.6016976214312839</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.521354280541459</v>
+        <v>0.6016976214312839</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5196574262666713</v>
+        <v>0.581176664633702</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5196574262666713</v>
+        <v>0.6019785924979766</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5203267703095094</v>
+        <v>0.5853097202563837</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5210431026877328</v>
+        <v>0.5796730379013667</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5017261021162012</v>
+        <v>0.5877814025922218</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4995771049815307</v>
+        <v>0.5858965949758921</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5038573587568996</v>
+        <v>0.5616760259759189</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4966825276272233</v>
+        <v>0.5594853147067737</v>
       </c>
     </row>
     <row r="73">
@@ -1150,177 +1150,177 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4951088978646199</v>
+        <v>0.5398154221470409</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4837708043252283</v>
+        <v>0.5060797152315086</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4811989121720885</v>
+        <v>0.5071959279333187</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4895484516864018</v>
+        <v>0.4870331373248486</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4908871397720778</v>
+        <v>0.4884658020812956</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4912453059611895</v>
+        <v>0.5171828670939729</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4916034721503013</v>
+        <v>0.5042658695910672</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4959307142610557</v>
+        <v>0.4910492015818767</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4934235509372734</v>
+        <v>0.4971663156925697</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4934235509372734</v>
+        <v>0.4946236713808433</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4978802507067429</v>
+        <v>0.4949818375699551</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4978802507067429</v>
+        <v>0.4756701111993341</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4985965830849664</v>
+        <v>0.4753119450102223</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4979272390421284</v>
+        <v>0.4673915336609091</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4989077609386927</v>
+        <v>0.4584781341219702</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4991427026156201</v>
+        <v>0.4690174259598087</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5009805218965643</v>
+        <v>0.4725281258750379</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5009805218965643</v>
+        <v>0.499390590058419</v>
       </c>
     </row>
   </sheetData>
